--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513088_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513088_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.348000000000001</v>
+        <v>8.057499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3638</v>
+        <v>5.5532</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9843</v>
+        <v>2.5042</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6254</v>
+        <v>1.63</v>
       </c>
       <c r="H2" t="n">
-        <v>1.592</v>
+        <v>1.6195</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0334</v>
+        <v>0.0105</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4592</v>
+        <v>2.5279</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2616</v>
+        <v>2.3291</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1976</v>
+        <v>0.1988</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8338</v>
+        <v>-0.8979</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6696</v>
+        <v>-0.7096</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1642</v>
+        <v>-0.1883</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1324</v>
+        <v>1.8324</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5676</v>
+        <v>0.6572</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5647</v>
+        <v>1.1752</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6798</v>
+        <v>6.14</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6483</v>
+        <v>4.2364</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0315</v>
+        <v>1.9037</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2196</v>
+        <v>6.2693</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9671</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2826</v>
+        <v>5.3022</v>
       </c>
       <c r="J3" t="n">
-        <v>6.068</v>
+        <v>6.1745</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2721</v>
+        <v>1.3407</v>
       </c>
       <c r="L3" t="n">
-        <v>4.7958</v>
+        <v>4.8339</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1517</v>
+        <v>0.0948</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3351</v>
+        <v>-0.3736</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4868</v>
+        <v>0.4684</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2423</v>
+        <v>0.6321</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4084</v>
+        <v>0.0379</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.5942</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2178</v>
+        <v>4.2904</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5455</v>
+        <v>3.2496</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6723</v>
+        <v>1.0407</v>
       </c>
       <c r="G4" t="n">
-        <v>5.2987</v>
+        <v>5.3278</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3427</v>
+        <v>0.3364</v>
       </c>
       <c r="I4" t="n">
-        <v>4.956</v>
+        <v>4.9914</v>
       </c>
       <c r="J4" t="n">
-        <v>5.519</v>
+        <v>5.5941</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2595</v>
+        <v>0.2759</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2595</v>
+        <v>5.3182</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2203</v>
+        <v>-0.2663</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0833</v>
+        <v>0.0605</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3035</v>
+        <v>-0.3267</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9748</v>
+        <v>0.0558</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6383</v>
+        <v>-0.0365</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3365</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6378</v>
+        <v>2.8649</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7994</v>
+        <v>1.7224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8384</v>
+        <v>1.1425</v>
       </c>
       <c r="G5" t="n">
-        <v>2.361</v>
+        <v>2.3791</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7143</v>
+        <v>1.7195</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6468</v>
+        <v>0.6596</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9862</v>
+        <v>2.0478</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5475</v>
+        <v>1.5797</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4387</v>
+        <v>0.468</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3749</v>
+        <v>0.3313</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1668</v>
+        <v>0.1398</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2081</v>
+        <v>0.1915</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.375</v>
+        <v>-0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6466</v>
+        <v>0.185</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7284</v>
+        <v>-0.355</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1602</v>
+        <v>0.2913</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4155</v>
+        <v>-0.592</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5757</v>
+        <v>0.8833</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3145</v>
+        <v>-1.3321</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8279</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4866</v>
+        <v>-0.502</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9042</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0227</v>
+        <v>-1.0088</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4103</v>
+        <v>-0.4425</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1949</v>
+        <v>0.1787</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6051</v>
+        <v>-0.6213</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1022</v>
+        <v>0.267</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2466</v>
+        <v>0.0466</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8555</v>
+        <v>0.2204</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0021</v>
+        <v>0.2247</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0204</v>
+        <v>2.3401</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0184</v>
+        <v>-2.1154</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3379</v>
+        <v>1.3226</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5184</v>
+        <v>0.5142</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8195</v>
+        <v>0.8085</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9908</v>
+        <v>1.0115</v>
       </c>
       <c r="K7" t="n">
-        <v>0.24</v>
+        <v>0.2561</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7508</v>
+        <v>0.7553</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3471</v>
+        <v>0.3111</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2784</v>
+        <v>0.258</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0687</v>
+        <v>0.0531</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6021</v>
+        <v>-0.3611</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.393</v>
+        <v>-0.1125</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2091</v>
+        <v>-0.2486</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8887</v>
+        <v>-1.5673</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.961</v>
+        <v>-2.008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0723</v>
+        <v>0.4407</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2252</v>
+        <v>-2.2598</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5635</v>
+        <v>-0.5916</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6617</v>
+        <v>-1.6683</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8146</v>
+        <v>-1.7985</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0781</v>
+        <v>0.079</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8927</v>
+        <v>-1.8775</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4106</v>
+        <v>-0.4614</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6415</v>
+        <v>-0.6706</v>
       </c>
       <c r="O8" t="n">
-        <v>0.231</v>
+        <v>0.2092</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4829</v>
+        <v>-0.1172</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0585</v>
+        <v>-0.0071</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5414</v>
+        <v>-0.1102</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5245</v>
+        <v>-2.0065</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8062</v>
+        <v>-3.8524</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2817</v>
+        <v>1.8459</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6075</v>
+        <v>-1.9031</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5534</v>
+        <v>0.5147</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.054</v>
+        <v>-2.4178</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5311</v>
+        <v>-2.5112</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9674</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5637</v>
+        <v>-2.6093</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0764</v>
+        <v>0.6081</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.586</v>
+        <v>0.4166</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5097</v>
+        <v>0.1915</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2533</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6873</v>
+        <v>-1.4172</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4339</v>
+        <v>1.0123</v>
       </c>
       <c r="S9" t="n">
-        <v>3.0328</v>
+        <v>0.3016</v>
       </c>
       <c r="T9" t="n">
-        <v>0.928</v>
+        <v>-0.1749</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1047</v>
+        <v>0.4765</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6965</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4841</v>
+        <v>0.2509</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1806</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7897</v>
+        <v>-2.275</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8577</v>
+        <v>-1.4822</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2359</v>
+        <v>-2.2378</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.9685</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2687</v>
+        <v>-1.2693</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.055</v>
+        <v>-1.0288</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2595</v>
+        <v>0.2759</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3145</v>
+        <v>-1.3047</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1809</v>
+        <v>-1.209</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2267</v>
+        <v>-1.2444</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0458</v>
+        <v>0.0354</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5538</v>
+        <v>-0.0372</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.393</v>
+        <v>-0.0485</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1608</v>
+        <v>0.0113</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9831</v>
+        <v>-3.7616</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7111</v>
+        <v>-4.135</v>
       </c>
       <c r="F11" t="n">
-        <v>1.728</v>
+        <v>0.3734</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8915</v>
+        <v>-4.1795</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5294</v>
+        <v>-2.392</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4209</v>
+        <v>-1.7875</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5451</v>
+        <v>-3.3217</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0838</v>
+        <v>-2.7091</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.629</v>
+        <v>-0.6126</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6536</v>
+        <v>-0.8578</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4455</v>
+        <v>0.3171</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2081</v>
+        <v>-1.1749</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4097</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.4339</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6819</v>
+        <v>0.4178</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9741</v>
+        <v>-0.052</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2923</v>
+        <v>0.4699</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3103</v>
+        <v>-3.7829</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5702</v>
+        <v>-5.1321</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2599</v>
+        <v>1.3493</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1745</v>
+        <v>-2.6322</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3943</v>
+        <v>-2.5689</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7803</v>
+        <v>-0.0633</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.3462</v>
+        <v>-2.488</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.7285</v>
+        <v>-1.9387</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6177</v>
+        <v>-0.5493</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8283</v>
+        <v>-0.1442</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3342</v>
+        <v>-0.6303</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1625</v>
+        <v>0.4861</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.227</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0242</v>
+        <v>-3.6441</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1357</v>
+        <v>1.7646</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4418</v>
+        <v>0.4981</v>
       </c>
       <c r="U12" t="n">
-        <v>0.306</v>
+        <v>1.2665</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2421</v>
+        <v>0.5019</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5494</v>
+        <v>8.4755</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9443</v>
+        <v>-0.1000000000000005</v>
       </c>
       <c r="F13" t="n">
-        <v>9.493699999999999</v>
+        <v>8.5755</v>
       </c>
       <c r="G13" t="n">
-        <v>2.393499999999999</v>
+        <v>2.384300000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.672499999999999</v>
+        <v>-1.6797</v>
       </c>
       <c r="I13" t="n">
-        <v>4.066100000000002</v>
+        <v>4.063999999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>4.827000000000004</v>
+        <v>5.318000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2835000000000005</v>
+        <v>0.5779000000000007</v>
       </c>
       <c r="L13" t="n">
-        <v>4.543299999999999</v>
+        <v>4.740099999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4333</v>
+        <v>-2.9338</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9558</v>
+        <v>-2.2578</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4771000000000001</v>
+        <v>-0.6759999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.2907</v>
+        <v>-12.1473</v>
       </c>
       <c r="R13" t="n">
-        <v>12.2906</v>
+        <v>12.1474</v>
       </c>
       <c r="S13" t="n">
-        <v>2.703500000000001</v>
+        <v>4.585800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0945</v>
+        <v>0.9933000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>3.797699999999999</v>
+        <v>3.5925</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4524</v>
+        <v>1.5056</v>
       </c>
       <c r="W13" t="n">
-        <v>5.6143</v>
+        <v>5.7357</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.161900000000001</v>
+        <v>-4.2301</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8697</v>
+        <v>2.8508</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7363</v>
+        <v>2.5031</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1334</v>
+        <v>0.3477</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6342</v>
+        <v>-1.657</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3427</v>
+        <v>-0.3364</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2914</v>
+        <v>-1.3206</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1178</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1192</v>
+        <v>-0.081</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1976</v>
+        <v>0.1988</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7125</v>
+        <v>-1.7747</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2235</v>
+        <v>-0.2553</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.489</v>
+        <v>-1.5194</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5039</v>
+        <v>0.5078</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2968</v>
+        <v>0.0049</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2071</v>
+        <v>0.5029</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,31 +1579,31 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8782</v>
+        <v>0.889</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8782</v>
+        <v>0.889</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7189</v>
+        <v>1.1927</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1846</v>
+        <v>-0.0796</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9035</v>
+        <v>1.2723</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2643</v>
+        <v>0.2784</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1479</v>
+        <v>0.1576</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1164</v>
+        <v>0.1207</v>
       </c>
       <c r="J16" t="n">
-        <v>0.424</v>
+        <v>0.483</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1583</v>
+        <v>-0.1205</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6036</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1596</v>
+        <v>-0.2047</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3062</v>
+        <v>0.2782</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7503</v>
+        <v>-0.2881</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4167</v>
+        <v>-0.3965</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3336</v>
+        <v>0.1083</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5859</v>
+        <v>0.0531</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6715</v>
+        <v>0.502</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2573</v>
+        <v>-0.4489</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1212</v>
+        <v>1.6995</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5013</v>
+        <v>1.1473</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6225</v>
+        <v>0.5522</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0968</v>
+        <v>1.1268</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0596</v>
+        <v>1.0075</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1564</v>
+        <v>0.1193</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0244</v>
+        <v>0.5727</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5583</v>
+        <v>0.1398</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4661</v>
+        <v>0.433</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2291</v>
+        <v>0.8098</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2533</v>
+        <v>0.8098</v>
       </c>
       <c r="S17" t="n">
-        <v>1.478</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2075</v>
+        <v>-0.6248</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2704</v>
+        <v>-0.0461</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.7853</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2421</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3644</v>
+        <v>-0.5365</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2623</v>
+        <v>-1.2039</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6267</v>
+        <v>0.6675</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7216</v>
+        <v>-2.1716</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1621</v>
+        <v>0.4757</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5595</v>
+        <v>-2.6473</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1138</v>
+        <v>-0.0598</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9953</v>
+        <v>1.0859</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1185</v>
+        <v>-1.1457</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6078</v>
+        <v>-2.1118</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1668</v>
+        <v>-0.6101</v>
       </c>
       <c r="O18" t="n">
-        <v>0.441</v>
+        <v>-1.5017</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8194</v>
+        <v>1.2147</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8194</v>
+        <v>2.227</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1345</v>
+        <v>0.4204</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8515</v>
+        <v>-0.3828</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.283</v>
+        <v>0.8033</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7709</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7709</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9619</v>
+        <v>-0.849</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3196</v>
+        <v>-2.0787</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3577</v>
+        <v>1.2298</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1075</v>
+        <v>-1.1112</v>
       </c>
       <c r="H19" t="n">
-        <v>0.34</v>
+        <v>0.3362</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4475</v>
+        <v>-1.4474</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0418</v>
+        <v>-1.0283</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3122</v>
+        <v>0.3161</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.354</v>
+        <v>-1.3444</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0658</v>
+        <v>-0.0829</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0278</v>
+        <v>0.0202</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0935</v>
+        <v>-0.103</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S19" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.1813</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2536</v>
+        <v>-0.0381</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3173</v>
+        <v>0.2194</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5209</v>
+        <v>-1.1854</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9571</v>
+        <v>-0.9843</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5638</v>
+        <v>-0.2011</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3614</v>
+        <v>-0.3494</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1043</v>
+        <v>-2.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7429</v>
+        <v>1.7463</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.225</v>
+        <v>-0.1813</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.6895</v>
+        <v>-2.6696</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4645</v>
+        <v>2.4883</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1364</v>
+        <v>-0.1682</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5738</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7216</v>
+        <v>-0.742</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.016</v>
+        <v>0.3058</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0501</v>
+        <v>-0.0417</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.3475</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8594</v>
+        <v>-1.5332</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1588</v>
+        <v>-1.689</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2994</v>
+        <v>0.1558</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6193</v>
+        <v>-1.5414</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1849</v>
+        <v>0.0195</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5656</v>
+        <v>-1.5609</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.571</v>
+        <v>-0.0484</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6024</v>
+        <v>0.7882</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0314</v>
+        <v>-0.8366</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0483</v>
+        <v>-1.493</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4175</v>
+        <v>-0.7687</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4658</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4097</v>
+        <v>0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6388</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5883</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5393</v>
+        <v>-0.8793</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.049</v>
+        <v>0.2477</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2421</v>
+        <v>0.4374</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2421</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.322</v>
+        <v>-1.7454</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3512</v>
+        <v>-3.1605</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0291</v>
+        <v>1.4151</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5605</v>
+        <v>-0.6233</v>
       </c>
       <c r="H22" t="n">
-        <v>0.014</v>
+        <v>-1.2048</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5745</v>
+        <v>0.5815</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1364</v>
+        <v>-0.518</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7393999999999999</v>
+        <v>-1.5824</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8758</v>
+        <v>1.0644</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4241</v>
+        <v>-0.1052</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7254</v>
+        <v>0.3776</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6987</v>
+        <v>-0.4829</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2048</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2291</v>
+        <v>1.6196</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4208</v>
+        <v>-0.4663</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4326</v>
+        <v>-0.618</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0118</v>
+        <v>0.1516</v>
       </c>
       <c r="V22" t="n">
-        <v>0.4544</v>
+        <v>-0.2509</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2124</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3943</v>
+        <v>-1.7772</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1518</v>
+        <v>-1.8182</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2425</v>
+        <v>0.041</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5341</v>
+        <v>2.5618</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5359</v>
+        <v>1.5416</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9982</v>
+        <v>1.0203</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7641</v>
+        <v>1.833</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5084</v>
+        <v>1.5402</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2556</v>
+        <v>0.2928</v>
       </c>
       <c r="M23" t="n">
-        <v>0.77</v>
+        <v>0.7288</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0275</v>
+        <v>0.0013</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7426</v>
+        <v>0.7275</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.663</v>
+        <v>-2.6319</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8427</v>
+        <v>-0.266</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8431</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0005</v>
+        <v>0.3484</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7719</v>
+        <v>-2.4336</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1686</v>
+        <v>-2.0516</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6032</v>
+        <v>-0.3819</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-0.9552</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7251</v>
+        <v>0.7499</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7054</v>
+        <v>-1.7051</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3469</v>
+        <v>-0.2762</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0321</v>
+        <v>1.0845</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.379</v>
+        <v>-1.3607</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6335</v>
+        <v>-0.6791</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.307</v>
+        <v>-0.3346</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3264</v>
+        <v>-0.3444</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0036</v>
+        <v>0.3192</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0154</v>
+        <v>-0.0019</v>
       </c>
       <c r="U24" t="n">
-        <v>0.019</v>
+        <v>0.3211</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.549399999999999</v>
+        <v>-4.4784</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.493699999999999</v>
+        <v>-8.5754</v>
       </c>
       <c r="F25" t="n">
-        <v>2.9442</v>
+        <v>4.097300000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3935</v>
+        <v>-2.384100000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6726</v>
+        <v>1.6798</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.066</v>
+        <v>-4.063999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4332</v>
+        <v>2.9339</v>
       </c>
       <c r="K25" t="n">
-        <v>1.9558</v>
+        <v>2.2579</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4773000000000003</v>
+        <v>0.6761000000000004</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.8268</v>
+        <v>-5.3181</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2832000000000002</v>
+        <v>-0.5778000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.543299999999999</v>
+        <v>-4.7401</v>
       </c>
       <c r="P25" t="n">
-        <v>0.000100000000000211</v>
+        <v>-0.0001000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.2907</v>
+        <v>-12.1473</v>
       </c>
       <c r="R25" t="n">
-        <v>12.2909</v>
+        <v>12.1471</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.7034</v>
+        <v>-0.5884</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.7978</v>
+        <v>-3.5926</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0943</v>
+        <v>3.0041</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4524</v>
+        <v>-1.5056</v>
       </c>
       <c r="W25" t="n">
-        <v>4.162000000000001</v>
+        <v>4.23</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.614299999999999</v>
+        <v>-5.7356</v>
       </c>
     </row>
   </sheetData>
